--- a/data/trans_dic/P6906-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6906-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño</t>
+          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,55; 43,91</t>
+          <t>20,62; 44,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,47; 51,28</t>
+          <t>25,33; 52,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,26; 62,7</t>
+          <t>31,27; 61,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,51; 43,06</t>
+          <t>14,61; 44,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,58; 39,73</t>
+          <t>14,84; 40,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,64; 47,47</t>
+          <t>19,39; 47,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,95; 55,62</t>
+          <t>25,31; 55,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,73; 47,66</t>
+          <t>26,06; 47,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,71; 38,94</t>
+          <t>20,98; 38,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,84; 45,71</t>
+          <t>25,84; 43,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,14; 54,34</t>
+          <t>32,35; 53,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23,85; 42,17</t>
+          <t>24,04; 41,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 36,27</t>
+          <t>9,63; 34,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,15; 43,14</t>
+          <t>14,83; 43,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,73; 54,84</t>
+          <t>15,01; 52,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,66; 36,48</t>
+          <t>9,42; 34,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,03; 37,61</t>
+          <t>12,55; 37,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 44,29</t>
+          <t>7,62; 41,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,71; 44,9</t>
+          <t>12,83; 43,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,91; 44,85</t>
+          <t>19,42; 46,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,9; 31,39</t>
+          <t>13,59; 32,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,27; 36,71</t>
+          <t>14,37; 36,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,95; 40,95</t>
+          <t>18,12; 42,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,89; 36,08</t>
+          <t>17,28; 34,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,95; 38,63</t>
+          <t>19,74; 39,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,23; 32,82</t>
+          <t>13,66; 32,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,17; 32,96</t>
+          <t>10,25; 32,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 35,0</t>
+          <t>8,51; 34,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,61</t>
+          <t>0,0; 38,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,06; 47,37</t>
+          <t>12,55; 45,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,0; 72,6</t>
+          <t>11,94; 80,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,86; 48,8</t>
+          <t>13,07; 47,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,74; 35,58</t>
+          <t>18,68; 35,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,07; 32,49</t>
+          <t>16,25; 32,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,78; 33,35</t>
+          <t>12,42; 33,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 32,25</t>
+          <t>12,46; 32,57</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,78; 27,15</t>
+          <t>14,91; 26,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,25; 31,93</t>
+          <t>15,45; 31,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,64; 31,38</t>
+          <t>17,12; 31,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,92; 29,63</t>
+          <t>14,42; 31,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,93; 39,76</t>
+          <t>15,83; 38,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,83; 42,64</t>
+          <t>19,98; 43,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,2; 45,58</t>
+          <t>24,41; 45,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,03; 32,62</t>
+          <t>18,38; 33,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,6; 26,88</t>
+          <t>16,53; 27,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,59; 32,32</t>
+          <t>18,64; 32,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,6; 33,84</t>
+          <t>22,28; 34,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,36; 29,36</t>
+          <t>17,87; 29,46</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 24,83</t>
+          <t>5,68; 23,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,89; 41,71</t>
+          <t>12,27; 41,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 19,61</t>
+          <t>3,89; 21,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 15,75</t>
+          <t>1,06; 16,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 27,31</t>
+          <t>9,09; 28,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,43; 50,98</t>
+          <t>19,03; 49,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,55; 40,07</t>
+          <t>14,74; 39,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 25,43</t>
+          <t>7,26; 26,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 22,64</t>
+          <t>9,37; 22,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,12; 40,76</t>
+          <t>20,17; 41,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 23,8</t>
+          <t>10,48; 24,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 19,73</t>
+          <t>6,72; 19,91</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -1417,221 +1417,80 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,99; 26,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,21; 30,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,04; 28,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,51; 24,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,43; 28,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,59; 36,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>25,81; 38,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>18,15; 29,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,12; 25,72</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,79; 31,91</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>23,44; 31,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,91; 25,48</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>22,59%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>25,97%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18,98%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>21,64%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>32,64%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>25,17%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>27,39%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>18,65; 26,87</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>20,88; 31,09</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19,25; 29,12</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14,76; 24,42</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>16,67; 27,49</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,69; 36,26</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>26,65; 39,62</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>18,06; 30,03</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>19,33; 25,67</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>23,65; 31,42</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>23,8; 31,32</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>18,15; 25,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
@@ -1647,7 +1506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño</t>
+          <t>Población quesu trabajo le afecta de manera que tiene problemas de sueño (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14026; 28575</t>
+          <t>13418; 28917</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14123; 28441</t>
+          <t>14046; 28901</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14197; 29414</t>
+          <t>14670; 28803</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7107; 19726</t>
+          <t>6693; 20472</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6802; 18534</t>
+          <t>6921; 18827</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8618; 20824</t>
+          <t>8504; 20758</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11460; 25546</t>
+          <t>11625; 25653</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15255; 28257</t>
+          <t>15451; 28420</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24257; 43513</t>
+          <t>23444; 42511</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25663; 45400</t>
+          <t>25663; 43590</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29839; 50448</t>
+          <t>30039; 50067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25070; 44323</t>
+          <t>25270; 43512</t>
         </is>
       </c>
     </row>
@@ -2135,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4015; 15360</t>
+          <t>4079; 14784</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5144; 15678</t>
+          <t>5390; 15626</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4757; 16582</t>
+          <t>4540; 15784</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4907; 18525</t>
+          <t>4783; 17757</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4588; 15653</t>
+          <t>5222; 15638</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2382; 11788</t>
+          <t>2028; 10992</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3737; 13199</t>
+          <t>3772; 12904</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8395; 18906</t>
+          <t>8187; 19569</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10832; 26358</t>
+          <t>11415; 26906</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9613; 23113</t>
+          <t>9045; 22900</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10106; 24421</t>
+          <t>10806; 25232</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15697; 33532</t>
+          <t>16063; 32306</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18955; 38638</t>
+          <t>19743; 39096</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10368; 25711</t>
+          <t>10705; 25349</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7474; 22047</t>
+          <t>6859; 21742</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5431; 20482</t>
+          <t>4979; 20150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6452</t>
+          <t>0; 6222</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4405; 15973</t>
+          <t>4231; 15218</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1148; 6947</t>
+          <t>1143; 7700</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2651; 8706</t>
+          <t>2331; 8421</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20630; 41385</t>
+          <t>21724; 41003</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18010; 36404</t>
+          <t>18210; 36430</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9769; 25497</t>
+          <t>9495; 25270</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9425; 24625</t>
+          <t>9517; 24871</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29691; 54523</t>
+          <t>29948; 53597</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17706; 37069</t>
+          <t>17932; 36260</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22777; 42953</t>
+          <t>23432; 43477</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18550; 39466</t>
+          <t>19210; 41531</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7955; 19861</t>
+          <t>7908; 19365</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13278; 28551</t>
+          <t>13377; 29368</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21186; 38320</t>
+          <t>20520; 38226</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20124; 34499</t>
+          <t>19444; 35409</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41623; 67407</t>
+          <t>41458; 68340</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34020; 59158</t>
+          <t>34124; 59126</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>47734; 74777</t>
+          <t>49226; 75384</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43879; 70154</t>
+          <t>42699; 70410</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2618,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3540; 15892</t>
+          <t>3634; 15054</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5557; 16687</t>
+          <t>4908; 16676</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2640; 13547</t>
+          <t>2690; 14838</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>544; 8058</t>
+          <t>540; 8409</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5834; 17922</t>
+          <t>5968; 18679</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8486; 22261</t>
+          <t>8312; 21746</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6884; 18965</t>
+          <t>6974; 18587</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9584; 32364</t>
+          <t>9243; 33739</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12368; 29346</t>
+          <t>12143; 28754</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16835; 34109</t>
+          <t>16872; 34408</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11325; 27703</t>
+          <t>12200; 28897</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12973; 35193</t>
+          <t>11988; 35515</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2831,62 +2690,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>140</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -2899,62 +2758,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106686</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84720</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83635</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64442</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47644</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63492</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70601</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88673</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154330</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148212</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154237</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153115</t>
         </is>
       </c>
     </row>
@@ -2967,282 +2826,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89686; 126337</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>69182; 100999</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66641; 100637</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>49279; 82439</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36169; 62153</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50686; 78378</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>55820; 83491</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63954; 105373</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>132408; 178065</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>128695; 172629</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>132743; 177122</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>123925; 176269</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>106686</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>84720</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>83635</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>64442</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>47644</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>63492</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>70601</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>88673</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>154330</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>148212</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>154237</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>153115</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>88075; 126925</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>68102; 101429</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>67365; 101921</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>50125; 82915</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>36699; 60513</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>50884; 77900</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>57639; 85697</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>63630; 105808</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>133854; 177728</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>127966; 169978</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>134773; 177346</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>125543; 177173</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
@@ -3252,7 +2903,6 @@
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P6906-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6906-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,62; 44,43</t>
+          <t>20,88; 44,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,33; 52,11</t>
+          <t>26,24; 53,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,27; 61,4</t>
+          <t>30,58; 61,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,61; 44,68</t>
+          <t>17,18; 47,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,84; 40,36</t>
+          <t>15,04; 40,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,39; 47,32</t>
+          <t>19,77; 48,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,31; 55,85</t>
+          <t>26,12; 55,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,06; 47,93</t>
+          <t>26,13; 47,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20,98; 38,05</t>
+          <t>20,55; 38,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25,84; 43,88</t>
+          <t>26,18; 45,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,35; 53,93</t>
+          <t>32,61; 54,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,04; 41,4</t>
+          <t>24,19; 41,75</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,63; 34,9</t>
+          <t>8,94; 35,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,83; 43,0</t>
+          <t>14,07; 42,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,01; 52,2</t>
+          <t>15,52; 51,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,42; 34,97</t>
+          <t>8,71; 34,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,55; 37,58</t>
+          <t>11,59; 37,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,62; 41,3</t>
+          <t>9,18; 42,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,83; 43,9</t>
+          <t>12,45; 43,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,42; 46,42</t>
+          <t>19,9; 45,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,59; 32,04</t>
+          <t>12,7; 31,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,37; 36,38</t>
+          <t>15,05; 37,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,12; 42,31</t>
+          <t>18,55; 41,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,28; 34,76</t>
+          <t>16,3; 34,2</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,74; 39,08</t>
+          <t>19,81; 39,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,66; 32,36</t>
+          <t>14,0; 33,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,25; 32,5</t>
+          <t>10,83; 31,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 34,43</t>
+          <t>10,41; 38,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,2</t>
+          <t>0,0; 45,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,55; 45,13</t>
+          <t>14,03; 46,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,94; 80,47</t>
+          <t>12,17; 72,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,07; 47,21</t>
+          <t>15,61; 48,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,68; 35,25</t>
+          <t>18,1; 36,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,25; 32,51</t>
+          <t>15,47; 32,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12,42; 33,05</t>
+          <t>13,17; 34,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,46; 32,57</t>
+          <t>12,82; 35,83</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,91; 26,69</t>
+          <t>14,76; 26,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,45; 31,24</t>
+          <t>16,04; 32,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,12; 31,77</t>
+          <t>16,49; 31,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 31,17</t>
+          <t>16,53; 32,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,83; 38,77</t>
+          <t>15,91; 39,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,98; 43,86</t>
+          <t>20,15; 41,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,41; 45,47</t>
+          <t>24,48; 45,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,38; 33,48</t>
+          <t>18,54; 33,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,53; 27,25</t>
+          <t>16,24; 27,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,64; 32,3</t>
+          <t>19,72; 32,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22,28; 34,12</t>
+          <t>21,94; 33,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,87; 29,46</t>
+          <t>19,59; 30,23</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 23,52</t>
+          <t>5,74; 24,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,27; 41,68</t>
+          <t>13,91; 43,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 21,47</t>
+          <t>3,5; 19,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 16,43</t>
+          <t>0,88; 13,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 28,46</t>
+          <t>9,04; 28,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,03; 49,8</t>
+          <t>18,44; 50,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,74; 39,28</t>
+          <t>13,59; 38,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 26,51</t>
+          <t>16,62; 30,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 22,18</t>
+          <t>9,43; 22,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,17; 41,12</t>
+          <t>19,39; 41,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,48; 24,82</t>
+          <t>9,83; 23,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 19,91</t>
+          <t>11,83; 21,11</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,99; 26,75</t>
+          <t>18,68; 26,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,21; 30,96</t>
+          <t>21,5; 31,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,04; 28,75</t>
+          <t>19,45; 29,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14,51; 24,28</t>
+          <t>15,29; 24,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,43; 28,24</t>
+          <t>16,67; 27,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,59; 36,48</t>
+          <t>23,1; 35,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,81; 38,6</t>
+          <t>26,98; 39,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,15; 29,91</t>
+          <t>24,05; 32,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,12; 25,72</t>
+          <t>19,21; 25,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,79; 31,91</t>
+          <t>23,55; 31,38</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23,44; 31,28</t>
+          <t>23,64; 31,07</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,91; 25,48</t>
+          <t>20,87; 27,23</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21652</t>
+          <t>22237</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34015</t>
+          <t>37189</t>
         </is>
       </c>
     </row>
@@ -1786,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13418; 28917</t>
+          <t>13590; 29252</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14046; 28901</t>
+          <t>14555; 29410</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14670; 28803</t>
+          <t>14345; 29014</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6693; 20472</t>
+          <t>8941; 24614</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6921; 18827</t>
+          <t>7018; 18999</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8504; 20758</t>
+          <t>8675; 21205</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11625; 25653</t>
+          <t>11999; 25423</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15451; 28420</t>
+          <t>16209; 29697</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>23444; 42511</t>
+          <t>22960; 42789</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25663; 43590</t>
+          <t>26006; 44894</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30039; 50067</t>
+          <t>30273; 51006</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25270; 43512</t>
+          <t>27591; 47623</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>9980</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13344</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23364</t>
+          <t>24194</t>
         </is>
       </c>
     </row>
@@ -1994,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4079; 14784</t>
+          <t>3786; 15237</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5390; 15626</t>
+          <t>5113; 15421</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4540; 15784</t>
+          <t>4693; 15702</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4783; 17757</t>
+          <t>4533; 18186</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5222; 15638</t>
+          <t>4821; 15462</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2028; 10992</t>
+          <t>2443; 11311</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3772; 12904</t>
+          <t>3659; 12825</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8187; 19569</t>
+          <t>9044; 20572</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11415; 26906</t>
+          <t>10661; 26532</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9045; 22900</t>
+          <t>9477; 23598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10806; 25232</t>
+          <t>11062; 24972</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16063; 32306</t>
+          <t>15897; 33346</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>12756</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15556</t>
+          <t>18872</t>
         </is>
       </c>
     </row>
@@ -2202,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19743; 39096</t>
+          <t>19813; 39599</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10705; 25349</t>
+          <t>10966; 26020</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6859; 21742</t>
+          <t>7246; 21374</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4979; 20150</t>
+          <t>6401; 23502</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6222</t>
+          <t>0; 7456</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4231; 15218</t>
+          <t>4731; 15527</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1143; 7700</t>
+          <t>1165; 6945</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2331; 8421</t>
+          <t>3193; 10011</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21724; 41003</t>
+          <t>21053; 41900</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18210; 36430</t>
+          <t>17332; 36343</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9495; 25270</t>
+          <t>10069; 26315</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9517; 24871</t>
+          <t>10502; 29361</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28707</t>
+          <t>36707</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>26836</t>
+          <t>29391</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55543</t>
+          <t>66099</t>
         </is>
       </c>
     </row>
@@ -2410,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29948; 53597</t>
+          <t>29633; 53397</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17932; 36260</t>
+          <t>18622; 37470</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23432; 43477</t>
+          <t>22573; 43576</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19210; 41531</t>
+          <t>25419; 49965</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7908; 19365</t>
+          <t>7948; 19926</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13377; 29368</t>
+          <t>13491; 27815</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20520; 38226</t>
+          <t>20585; 37983</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19444; 35409</t>
+          <t>21097; 37742</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41458; 68340</t>
+          <t>40734; 68229</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34124; 59126</t>
+          <t>36091; 59198</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49226; 75384</t>
+          <t>48468; 74983</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42699; 70410</t>
+          <t>52409; 80861</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24637</t>
+          <t>26572</t>
         </is>
       </c>
     </row>
@@ -2618,62 +2618,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3634; 15054</t>
+          <t>3677; 15837</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4908; 16676</t>
+          <t>5564; 17254</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2690; 14838</t>
+          <t>2415; 13747</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>540; 8409</t>
+          <t>581; 8669</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5968; 18679</t>
+          <t>5935; 18690</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8312; 21746</t>
+          <t>8054; 21893</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6974; 18587</t>
+          <t>6432; 18403</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9243; 33739</t>
+          <t>16896; 31467</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12143; 28754</t>
+          <t>12225; 29137</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16872; 34408</t>
+          <t>16223; 34593</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12200; 28897</t>
+          <t>11448; 27558</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11988; 35515</t>
+          <t>19790; 35320</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64442</t>
+          <t>77437</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>88673</t>
+          <t>95489</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>153115</t>
+          <t>172927</t>
         </is>
       </c>
     </row>
@@ -2826,62 +2826,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>89686; 126337</t>
+          <t>88246; 126617</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>69182; 100999</t>
+          <t>70136; 102828</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66641; 100637</t>
+          <t>68077; 101494</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49279; 82439</t>
+          <t>58875; 94842</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36169; 62153</t>
+          <t>36686; 60996</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50686; 78378</t>
+          <t>49624; 77038</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>55820; 83491</t>
+          <t>58361; 85372</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>63954; 105373</t>
+          <t>82566; 110520</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>132408; 178065</t>
+          <t>133037; 179563</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>128695; 172629</t>
+          <t>127406; 169802</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>132743; 177122</t>
+          <t>133864; 175950</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>123925; 176269</t>
+          <t>151976; 198343</t>
         </is>
       </c>
     </row>
